--- a/docs/project/Lab_03_rubric.xlsx
+++ b/docs/project/Lab_03_rubric.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -642,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.1640625" customWidth="1"/>
@@ -669,12 +669,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
+    <row r="2" spans="1:8" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1.1 Restate Your Selected Project</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Correct project row (question, population, variables, composite score) from Lab 2's table accurately copied/restated</t>
+        </is>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -682,22 +686,32 @@
       <c r="D2" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Sections</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1.1 Restate Your Selected Project</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Included near the start of the document for reference</t>
+        </is>
       </c>
       <c r="C3" s="2">
         <v>0.5</v>
@@ -705,24 +719,28 @@
       <c r="D3" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>4</v>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>1.1 Restate Your Selected Project</t>
+        </is>
       </c>
       <c r="G3" s="7">
         <f>SUM(IF($D$2=FALSE(),0,1)*$C$2,IF($D$3=FALSE(),0,1)*$C$3)</f>
-        <v>0</v>
       </c>
       <c r="H3" s="8">
         <f>SUM($C$2:$C$3)</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>1.2 Import Your Saved Data from Lab 2</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>import() from the rio package, with which = "wbns_04_no_na", used to import the .rda file exported at the end of Lab 2</t>
+        </is>
       </c>
       <c r="C4" s="9">
         <v>1</v>
@@ -730,24 +748,28 @@
       <c r="D4" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>10</v>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>1.2 Import Your Saved Data from Lab 2</t>
+        </is>
       </c>
       <c r="G4" s="7">
         <f>SUM(IF($D$4=FALSE(),0,1)*$C$4,IF($D$5=FALSE(),0,1)*$C$5,IF($D$6=FALSE(),0,1)*$C$6)</f>
-        <v>0</v>
       </c>
       <c r="H4" s="8">
         <f>SUM($C$4:$C$6)</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>1.2 Import Your Saved Data from Lab 2</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Result saved as an object called wbns_04_no_na</t>
+        </is>
       </c>
       <c r="C5" s="9">
         <v>0.5</v>
@@ -755,24 +777,28 @@
       <c r="D5" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>13</v>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>1.3 Constructing the Composite Score</t>
+        </is>
       </c>
       <c r="G5" s="7">
-        <f>SUM(IF($D$7=FALSE(),0,1)*$C$7,IF($D$8=FALSE(),0,1)*$C$8,IF($D$9=FALSE(),0,1)*$C$9)</f>
-        <v>0</v>
+        <f>SUM(IF($D$7=FALSE(),0,1)*$C$7,IF($D$8=FALSE(),0,1)*$C$8,IF($D$9=FALSE(),0,1)*$C$9,IF($D$10=FALSE(),0,1)*$C$10,IF($D$11=FALSE(),0,1)*$C$11)</f>
       </c>
       <c r="H5" s="8">
-        <f>SUM($C$7:$C$9)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>14</v>
+        <f>SUM($C$7:$C$11)</f>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>1.2 Import Your Saved Data from Lab 2</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Number of rows and columns printed (dim()) to verify the import</t>
+        </is>
       </c>
       <c r="C6" s="9">
         <v>1</v>
@@ -780,149 +806,173 @@
       <c r="D6" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>15</v>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>1.4 Quick Summaries of Your Variables</t>
+        </is>
       </c>
       <c r="G6" s="7">
-        <f>SUM(IF($D$10=FALSE(),0,1)*$C$10,IF($D$11=FALSE(),0,1)*$C$11,IF($D$12=FALSE(),0,1)*$C$12)</f>
-        <v>0</v>
+        <f>SUM(IF($D$12=FALSE(),0,1)*$C$12,IF($D$13=FALSE(),0,1)*$C$13,IF($D$14=FALSE(),0,1)*$C$14)</f>
       </c>
       <c r="H6" s="8">
-        <f>SUM($C$10:$C$12)</f>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
+        <f>SUM($C$12:$C$14)</f>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="50" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1.3 Constructing the Composite Score</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Items converted to numbers with case_when() per the questionnaire scale (not as.numeric()); correct direction; Project 3 combines skipped pairs correctly and drops rows where total_benefits is NA</t>
+        </is>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>17</v>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>1.5 Creating Categorical Versions of Composite Score(s)</t>
+        </is>
       </c>
       <c r="G7" s="7">
-        <f>SUM(IF($D$13=FALSE(),0,1)*$C$13,IF($D$14=FALSE(),0,1)*$C$14,IF($D$15=FALSE(),0,1)*$C$15)</f>
-        <v>0</v>
+        <f>SUM(IF($D$15=FALSE(),0,1)*$C$15,IF($D$16=FALSE(),0,1)*$C$16,IF($D$17=FALSE(),0,1)*$C$17)</f>
       </c>
       <c r="H7" s="8">
-        <f>SUM($C$13:$C$15)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
+        <f>SUM($C$15:$C$17)</f>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="50" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>1.3 Constructing the Composite Score</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Composite variable(s) created with mutate() using the required name(s): ease_free_food / trust_courtesy_respect / mental_health_score and total_benefits</t>
+        </is>
       </c>
       <c r="C8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="D8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>1.6 Building a Summary Table</t>
+        </is>
+      </c>
+      <c r="G8" s="7">
+        <f>SUM(IF($D$18=FALSE(),0,1)*$C$18,IF($D$19=FALSE(),0,1)*$C$19,IF($D$20=FALSE(),0,1)*$C$20)</f>
+      </c>
+      <c r="H8" s="8">
+        <f>SUM($C$18:$C$20)</f>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1.3 Constructing the Composite Score</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Result saved as a new object called wbns_05_composite</t>
+        </is>
+      </c>
+      <c r="C9" s="2">
         <v>0.5</v>
       </c>
-      <c r="D8" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="7">
-        <f>SUM(IF($D$16=FALSE(),0,1)*$C$16,IF($D$17=FALSE(),0,1)*$C$17)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="8">
-        <f>SUM($C$16:$C$17)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="D9" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>1.7 Grouped Summaries</t>
+        </is>
+      </c>
+      <c r="G9" s="7">
+        <f>SUM(IF($D$21=FALSE(),0,1)*$C$21,IF($D$22=FALSE(),0,1)*$C$22)</f>
+      </c>
+      <c r="H9" s="8">
+        <f>SUM($C$21:$C$22)</f>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>1.3 Constructing the Composite Score</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>At least two converted (_num) variables checked against the originals with tabyl()</t>
+        </is>
+      </c>
+      <c r="C10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>1.8 Export Tables</t>
+        </is>
+      </c>
+      <c r="G10" s="7">
+        <f>SUM(IF($D$23=FALSE(),0,1)*$C$23,IF($D$24=FALSE(),0,1)*$C$24)</f>
+      </c>
+      <c r="H10" s="8">
+        <f>SUM($C$23:$C$24)</f>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="50" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>1.3 Constructing the Composite Score</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>summary() of composite variable(s) displayed, with 1-2 sentences confirming the range and direction make sense (Project 3: direction and WIC choice stated)</t>
+        </is>
+      </c>
+      <c r="C11" s="2">
         <v>1.5</v>
       </c>
-      <c r="D9" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="7">
-        <f>SUM(IF($D$18=FALSE(),0,1)*$C$18,IF($D$19=FALSE(),0,1)*$C$19)</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
-        <f>SUM($C$18:$C$19)</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="9">
-        <v>2</v>
-      </c>
-      <c r="D10" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="7">
-        <f>SUM(IF($D$20=FALSE(),0,1)*$C$20,IF($D$21=FALSE(),0,1)*$C$21,IF($D$22=FALSE(),0,1)*$C$22,IF($D$23=FALSE(),0,1)*$C$23)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
-        <f>SUM($C$20:$C$23)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="D11" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="11">
-        <f>SUM(G3:G10)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="12">
-        <f>SUM(H3:H10)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>26</v>
+      <c r="D11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>General / Document Quality</t>
+        </is>
+      </c>
+      <c r="G11" s="7">
+        <f>SUM(IF($D$25=FALSE(),0,1)*$C$25,IF($D$26=FALSE(),0,1)*$C$26,IF($D$27=FALSE(),0,1)*$C$27,IF($D$28=FALSE(),0,1)*$C$28)</f>
+      </c>
+      <c r="H11" s="8">
+        <f>SUM($C$25:$C$28)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>1.4 Quick Summaries of Your Variables</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>skim() used on wbns_05_composite to summarize main variables and composite score(s)</t>
+        </is>
       </c>
       <c r="C12" s="9">
         <v>1</v>
@@ -930,158 +980,303 @@
       <c r="D12" s="15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G12" s="11">
+        <f>SUM(G3:G11)</f>
+      </c>
+      <c r="H12" s="12">
+        <f>SUM(H3:H11)</f>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>1.4 Quick Summaries of Your Variables</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Result saved as a new object called quick_summaries and printed</t>
+        </is>
+      </c>
+      <c r="C13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>1.4 Quick Summaries of Your Variables</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Unexpected values, missing data, or other issues identified and addressed (or explicitly noted)</t>
+        </is>
+      </c>
+      <c r="C14" s="9">
         <v>1.5</v>
       </c>
-      <c r="D13" s="13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="D14" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>1.5 Creating Categorical Versions of Composite Score(s)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>mutate() with case_when() or cut() used to create a categorical version of each composite score, with meaningful category labels</t>
+        </is>
+      </c>
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>1.5 Creating Categorical Versions of Composite Score(s)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Result saved as a new object called wbns_06_cat</t>
+        </is>
+      </c>
+      <c r="C16" s="2">
         <v>0.5</v>
       </c>
-      <c r="D14" s="13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="D16" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>1.5 Creating Categorical Versions of Composite Score(s)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>tabyl() or count() used to display category counts and confirm no one was left out (e.g., unexpected NA)</t>
+        </is>
+      </c>
+      <c r="C17" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="9">
+      <c r="D17" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>1.6 Building a Summary Table</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>tbl_summary() used to build an overall summary table of the composite score(s) and the correct project-specific main variable(s)</t>
+        </is>
+      </c>
+      <c r="C18" s="9">
         <v>1.5</v>
       </c>
-      <c r="D16" s="15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="9">
+      <c r="D18" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>1.6 Building a Summary Table</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Result saved as a new object called summary_table_overall and displayed</t>
+        </is>
+      </c>
+      <c r="C19" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>1.6 Building a Summary Table</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>At least one customization made to the table's appearance or labels (e.g., modify_header(), relabeling)</t>
+        </is>
+      </c>
+      <c r="C20" s="9">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>1.7 Grouped Summaries</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>group_by() and get_summary_stats() used to calculate composite score summary statistics by the correct grouping variable</t>
+        </is>
+      </c>
+      <c r="C21" s="2">
         <v>1.5</v>
       </c>
-      <c r="D17" s="15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="D21" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>1.7 Grouped Summaries</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2-3 sentences written interpreting differences across groups and relating them back to the project question</t>
+        </is>
+      </c>
+      <c r="C22" s="2">
         <v>1.5</v>
       </c>
-      <c r="D18" s="13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="D22" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>1.8 Export Tables</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>export() from the rio package used to save wbns_06_cat and summary_table_overall in a .rda file</t>
+        </is>
+      </c>
+      <c r="C23" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="D23" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>1.8 Export Tables</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>File saved in the data_project folder with a clear, identifiable file name</t>
+        </is>
+      </c>
+      <c r="C24" s="9">
         <v>1</v>
       </c>
-      <c r="D19" s="13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="9">
+      <c r="D24" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>General / Document Quality</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Editing file is the correct, unmodified .qmd template -- no instructional text/sections deleted</t>
+        </is>
+      </c>
+      <c r="C25" s="2">
         <v>0.5</v>
       </c>
-      <c r="D20" s="15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="D25" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>General / Document Quality</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>File renders (knits) without errors</t>
+        </is>
+      </c>
+      <c r="C26" s="2">
         <v>0.5</v>
       </c>
-      <c r="D21" s="15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="9">
+      <c r="D26" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>General / Document Quality</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>File follows naming convention: lastname_firstinit_lab_03.qmd</t>
+        </is>
+      </c>
+      <c r="C27" s="2">
         <v>0.5</v>
       </c>
-      <c r="D22" s="15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="9">
+      <c r="D27" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>General / Document Quality</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Code is reasonably readable/organized (chunks labeled, no leftover scratch code)</t>
+        </is>
+      </c>
+      <c r="C28" s="2">
         <v>0.5</v>
       </c>
-      <c r="D23" s="15" t="b">
+      <c r="D28" s="13" t="b">
         <v>0</v>
       </c>
     </row>
